--- a/server/ATS/template/srms_template.xlsx
+++ b/server/ATS/template/srms_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\server\ATS\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66841152-E8CC-4C03-96A7-7D7F0E566A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B0CA84-55E9-47D6-BADB-9B1168FE3D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94096412-2FEB-4621-AAB3-520197C8C40C}"/>
   </bookViews>
@@ -885,7 +885,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -931,6 +931,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -943,17 +945,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1316,22 +1322,22 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1387,10 +1393,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="21"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
@@ -1546,24 +1552,24 @@
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="32" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="33"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/server/ATS/template/srms_template.xlsx
+++ b/server/ATS/template/srms_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\server\ATS\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B0CA84-55E9-47D6-BADB-9B1168FE3D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2CA940-21B5-4D4E-BBA5-F74B016F6DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94096412-2FEB-4621-AAB3-520197C8C40C}"/>
   </bookViews>
@@ -933,6 +933,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -953,12 +959,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1323,21 +1323,21 @@
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.21875" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="31.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1393,10 +1393,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="21"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
@@ -1552,22 +1552,22 @@
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="34" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="31"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="25"/>
       <c r="F27" s="26"/>
     </row>
